--- a/data/trans_orig/IP19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Habitat-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79352</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100114</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118859</t>
+          <t>119004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185201</t>
+          <t>185232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211099</t>
+          <t>210460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>34073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80704</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106602</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116271</t>
+          <t>115961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>135910</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129969</t>
+          <t>130120</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>151954</t>
+          <t>152255</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254499</t>
+          <t>252845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>283269</t>
+          <t>284950</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78201</t>
+          <t>78511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>82022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123345</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152115</t>
+          <t>153769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91552</t>
+          <t>92459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107814</t>
+          <t>108086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95550</t>
+          <t>96066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>113819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193748</t>
+          <t>193343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217847</t>
+          <t>218664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>45358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>53591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>94131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131061</t>
+          <t>130870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154105</t>
+          <t>153809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143806</t>
+          <t>144179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>164692</t>
+          <t>163785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281746</t>
+          <t>283675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312053</t>
+          <t>313334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>63645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105086</t>
+          <t>103805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>133464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>87321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106182</t>
+          <t>107342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95652</t>
+          <t>95265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114597</t>
+          <t>114498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188807</t>
+          <t>187965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215144</t>
+          <t>215638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51248</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59032</t>
+          <t>59419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>78403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125524</t>
+          <t>126401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146912</t>
+          <t>148045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>147008</t>
+          <t>146664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168661</t>
+          <t>168399</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>276687</t>
+          <t>277796</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308955</t>
+          <t>308438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>58313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>79957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76255</t>
+          <t>76599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152934</t>
+          <t>151825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100725</t>
+          <t>99913</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117664</t>
+          <t>117594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105629</t>
+          <t>106378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125094</t>
+          <t>124328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211827</t>
+          <t>211076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237907</t>
+          <t>237739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59535</t>
+          <t>58786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82633</t>
+          <t>82801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108713</t>
+          <t>109464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137310</t>
+          <t>138222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>160925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141909</t>
+          <t>141718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163148</t>
+          <t>163136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287524</t>
+          <t>286696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>316715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49588</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72990</t>
+          <t>72078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64380</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>99874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129065</t>
+          <t>129893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82881</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>101190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>92868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181469</t>
+          <t>181695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>207371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55101</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>74412</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100314</t>
+          <t>100088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132006</t>
+          <t>132215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151641</t>
+          <t>152888</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146751</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>170251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>284457</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315916</t>
+          <t>315700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>54359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75241</t>
+          <t>75032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115690</t>
+          <t>115906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146569</t>
+          <t>147149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>101463</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119319</t>
+          <t>118860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109591</t>
+          <t>109332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127790</t>
+          <t>128441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216575</t>
+          <t>215133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243430</t>
+          <t>242300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54277</t>
+          <t>54534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57082</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>80370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106095</t>
+          <t>107537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132114</t>
+          <t>134082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>155455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142563</t>
+          <t>143048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163604</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281849</t>
+          <t>283294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313462</t>
+          <t>314384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75306</t>
+          <t>73338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42132</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63173</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>98772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>49711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37027</t>
+          <t>35738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64401</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76014</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107374</t>
+          <t>107467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49341</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>61528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73908</t>
+          <t>74993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105349</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>66374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>59989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100587</t>
+          <t>99553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85798</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62159</t>
+          <t>63205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88380</t>
+          <t>88596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130594</t>
+          <t>128984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165950</t>
+          <t>165239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56215</t>
+          <t>56975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79944</t>
+          <t>81131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84525</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116001</t>
+          <t>115474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>151666</t>
+          <t>151225</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>188474</t>
+          <t>189161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58488</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89885</t>
+          <t>89408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105421</t>
+          <t>106893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140675</t>
+          <t>141170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>63172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115123</t>
+          <t>116088</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>64590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129783</t>
+          <t>125012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>61143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87642</t>
+          <t>89097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136016</t>
+          <t>136151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206122</t>
+          <t>212102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>30912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>46839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75634</t>
+          <t>75075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132052</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44076</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64594</t>
+          <t>63828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71417</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98829</t>
+          <t>98223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127826</t>
+          <t>127696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65435</t>
+          <t>65355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70592</t>
+          <t>71428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97989</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128637</t>
+          <t>130952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66004</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47782</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71312</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>100145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129638</t>
+          <t>130371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183798</t>
+          <t>183500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208229</t>
+          <t>204326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259232</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>410612</t>
+          <t>409931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482949</t>
+          <t>482342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222501</t>
+          <t>224188</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>311047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>256510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>310574</t>
+          <t>309886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>494285</t>
+          <t>496703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>597464</t>
+          <t>596245</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109752</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>118167</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88724</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79032</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>97435</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>97223</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109752</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>100544</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>119004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185232</t>
+          <t>186583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210460</t>
+          <t>210621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52458</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>50002</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41291</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>59694</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>41503</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>59905</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>36,04%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43325</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34073</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52533</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>81182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106571</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141823</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>130320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>153469</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>61,43%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126668</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>115961</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>135910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>115900</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>137086</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>65,13%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>59,63%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141823</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>130120</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>152255</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>66,85%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252845</t>
+          <t>253800</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>284950</t>
+          <t>283141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -1410,67 +1410,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>70319</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58673</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81822</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>67804</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58562</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78511</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57386</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>78572</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70319</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>59887</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82022</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>123473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153769</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>194472</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>194472</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>194472</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>105540</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96456</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>100496</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>92459</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108086</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>92526</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>108791</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>105540</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>96066</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>113819</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193343</t>
+          <t>194494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218664</t>
+          <t>217767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44117</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35861</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53201</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>37321</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29731</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45358</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>29026</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>45291</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44117</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35838</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>53591</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94131</t>
+          <t>92980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>154261</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>142995</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>163582</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>74,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>143131</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130870</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>153809</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130691</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>153876</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>154261</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>144179</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>163785</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>74,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283675</t>
+          <t>281309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313334</t>
+          <t>311648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>53563</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44242</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>66184</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>55506</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>78445</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>55439</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>78624</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>31,62%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>53563</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44039</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>63645</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103805</t>
+          <t>105491</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133464</t>
+          <t>135830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2660,72 +2660,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>511376</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>491898</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>530917</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>511376</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>490910</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>529383</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>70,76%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>940082</t>
+          <t>942885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>994693</t>
+          <t>997250</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -2773,72 +2773,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191783</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>230802</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>193317</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>231790</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408337</t>
+          <t>405780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462948</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -2886,57 +2886,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3348,72 +3348,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104930</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>94758</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113707</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97354</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87321</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>107342</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>87113</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105606</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>104930</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95265</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114498</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187965</t>
+          <t>189552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215638</t>
+          <t>216389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -3461,72 +3461,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49754</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40977</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>59926</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32,16%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>42003</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52036</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>33751</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>52244</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49754</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>40186</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>59419</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>32,16%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>77652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106076</t>
+          <t>104489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -3574,57 +3574,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3804,72 +3804,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>158168</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>145939</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>168991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>70,84%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>65,37%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>75,69%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>136536</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126401</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>148045</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>125670</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>147163</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>66,16%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>61,25%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>158168</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>146664</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>168399</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>70,84%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>277796</t>
+          <t>278021</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308438</t>
+          <t>309177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -3917,72 +3917,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65095</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54272</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77324</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69822</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58313</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>79957</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>59195</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>80688</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>65095</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>54864</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76599</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151825</t>
+          <t>151600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -4030,57 +4030,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4260,72 +4260,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115539</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105291</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>109025</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>99913</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>117594</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>99742</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>117674</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>70,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>115539</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>106378</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>124328</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211076</t>
+          <t>210466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237739</t>
+          <t>236199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -4378,67 +4378,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>49625</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39927</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59873</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>36,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>46351</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37782</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55463</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>55634</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>29,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49625</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>40836</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>58786</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>110074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -4486,57 +4486,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4716,72 +4716,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>153360</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141970</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>164353</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149431</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>138222</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>160925</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>138332</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>160833</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>71,06%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>153360</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>141718</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>163136</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286696</t>
+          <t>287069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316715</t>
+          <t>318726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -4829,72 +4829,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52929</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41936</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>64319</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>60869</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>49375</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>72078</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>49467</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>71968</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>28,94%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>52929</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>43153</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>64571</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>97863</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129893</t>
+          <t>129520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -4942,57 +4942,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5172,72 +5172,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>531997</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>513172</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>552398</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>531997</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>512186</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>552389</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>992301</t>
+          <t>997221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1050824</t>
+          <t>1053005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -5285,72 +5285,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>197002</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>236228</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>197011</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>237214</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>407786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>468490</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -5398,57 +5398,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5579,7 +5579,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5860,72 +5860,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>102658</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92738</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111777</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>93056</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84122</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>101190</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>83360</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101870</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>102658</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92868</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>111840</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181695</t>
+          <t>182020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207371</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -5973,72 +5973,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45418</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36299</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55338</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40651</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32517</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>49585</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>31837</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>50347</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,4%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,08%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>45418</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>36236</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>55208</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74412</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100088</t>
+          <t>99763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -6086,57 +6086,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6316,72 +6316,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>158652</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>147882</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>169597</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>70,71%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>65,91%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>142384</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>132215</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>152888</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>130747</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>153045</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>68,7%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>73,77%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>158652</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>147683</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>170251</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>284457</t>
+          <t>284974</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315700</t>
+          <t>315486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -6429,72 +6429,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65707</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54762</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76477</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64863</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54359</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75032</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54202</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76500</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>65707</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>54108</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76676</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115906</t>
+          <t>116120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147149</t>
+          <t>146632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -6542,57 +6542,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6772,72 +6772,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>119284</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>108295</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>127562</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>110803</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>101463</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118860</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>100950</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>118715</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>119284</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>109332</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>128441</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215133</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242300</t>
+          <t>241790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -6885,72 +6885,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47389</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39111</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58378</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>45194</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37137</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54534</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37282</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>55047</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47389</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>38232</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>57341</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80370</t>
+          <t>80880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107537</t>
+          <t>106269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -6998,57 +6998,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7228,72 +7228,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>153537</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>164064</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>144833</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>134082</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>155455</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>133704</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>156436</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>153537</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143048</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>164032</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283294</t>
+          <t>283444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314384</t>
+          <t>313434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -7341,72 +7341,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52199</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41672</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>62142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>62587</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51965</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>73338</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>50984</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>73716</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>30,17%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>52199</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>41704</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>62688</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98772</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129862</t>
+          <t>129712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -7454,57 +7454,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7684,72 +7684,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -7797,72 +7797,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -7910,57 +7910,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8091,7 +8091,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8259,72 +8259,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39922</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30060</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51133</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41359</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33077</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49711</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>91278</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75521</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107467</t>
+          <t>92243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -8372,72 +8372,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48873</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35736</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60939</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41215</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33243</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50752</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90147</t>
+          <t>94124</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74993</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>109334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -8485,72 +8485,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36525</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25848</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55904</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34705</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26097</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42487</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>44408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>75726</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99553</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -8598,57 +8598,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8715,72 +8715,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63329</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75634</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>71178</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59793</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>86120</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63205</t>
+          <t>51026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88596</t>
+          <t>71864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>145686</t>
+          <t>124891</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128984</t>
+          <t>107968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165239</t>
+          <t>140159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -8828,72 +8828,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96347</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>81113</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111336</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>47,87%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>68573</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>56975</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>81131</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>36,57%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>30,38%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>43,27%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>72097</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85291</t>
+          <t>61021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115474</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>169180</t>
+          <t>168444</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>151225</t>
+          <t>150438</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189161</t>
+          <t>187689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -8941,72 +8941,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72909</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60221</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88300</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47766</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37541</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59153</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75349</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89408</t>
+          <t>57861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123114</t>
+          <t>120552</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106893</t>
+          <t>103777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>137360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -9054,57 +9054,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9171,72 +9171,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40184</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30290</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49933</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,33%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>49769</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28662</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>63172</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,79%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47852</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59165</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>97622</t>
+          <t>85080</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116088</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -9284,72 +9284,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68367</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55715</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81724</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>85931</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64590</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125012</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74224</t>
+          <t>55467</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61143</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89097</t>
+          <t>67007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160155</t>
+          <t>123835</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136151</t>
+          <t>107836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212102</t>
+          <t>141573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -9397,72 +9397,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56587</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44760</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71744</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51273</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30912</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>64367</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59978</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75075</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>109813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85759</t>
+          <t>93724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131230</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -9510,57 +9510,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9627,72 +9627,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54668</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45700</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65270</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>32,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>53495</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43370</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>63828</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59819</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49401</t>
+          <t>42363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113314</t>
+          <t>106905</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98223</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127696</t>
+          <t>122488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -9740,72 +9740,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57143</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>46964</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69029</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>54442</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>44421</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>65355</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71428</t>
+          <t>65781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>113510</t>
+          <t>111989</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>98213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130952</t>
+          <t>127221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -9853,72 +9853,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>54478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44173</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>65154</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>55469</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>46199</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>66013</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70530</t>
+          <t>66414</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>95405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130371</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -9966,57 +9966,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10083,72 +10083,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>198104</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>179474</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>220135</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>215801</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>183500</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>237122</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>232097</t>
+          <t>198436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204326</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>218221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>447898</t>
+          <t>396540</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409931</t>
+          <t>367710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482342</t>
+          <t>424287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -10196,72 +10196,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270730</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>246452</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>296043</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>42,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>250161</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>224188</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>311047</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>282829</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256510</t>
+          <t>207187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309886</t>
+          <t>249535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>532991</t>
+          <t>498391</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>496703</t>
+          <t>465133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>596245</t>
+          <t>534515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -10309,72 +10309,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -10422,57 +10422,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
